--- a/public/集单池上传模板.xlsx
+++ b/public/集单池上传模板.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="集单池模板" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,10 +415,13 @@
       <c r="C1" t="str">
         <v>核查量</v>
       </c>
+      <c r="D1" t="str">
+        <v>城市群</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>